--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.85830107114147</v>
+        <v>2.901973924060489</v>
       </c>
       <c r="D2" t="n">
-        <v>18.3290135559581</v>
+        <v>2.978464702843192</v>
       </c>
       <c r="E2" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F2" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.21881851530904</v>
+        <v>1.985558008737719</v>
       </c>
       <c r="D3" t="n">
-        <v>11.77522294854953</v>
+        <v>1.913473729139298</v>
       </c>
       <c r="E3" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F3" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.472854184859584</v>
+        <v>1.051838805039683</v>
       </c>
       <c r="D4" t="n">
-        <v>6.303227002356532</v>
+        <v>1.024274387882936</v>
       </c>
       <c r="E4" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F4" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.6632446120305</v>
+        <v>9.532777249454957</v>
       </c>
       <c r="D5" t="n">
-        <v>58.37869684133936</v>
+        <v>9.486538236717646</v>
       </c>
       <c r="E5" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F5" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.93669522529096</v>
+        <v>2.589712974109781</v>
       </c>
       <c r="D6" t="n">
-        <v>15.44248654829952</v>
+        <v>2.509404064098673</v>
       </c>
       <c r="E6" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F6" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.69738699282873</v>
+        <v>8.40082538633467</v>
       </c>
       <c r="D7" t="n">
-        <v>51.17174405735761</v>
+        <v>8.315408409320611</v>
       </c>
       <c r="E7" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F7" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.60063841461136</v>
+        <v>2.535103742374346</v>
       </c>
       <c r="D8" t="n">
-        <v>15.1624112065412</v>
+        <v>2.463891821062944</v>
       </c>
       <c r="E8" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F8" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.91985408468514</v>
+        <v>5.511976288761335</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05616211522401</v>
+        <v>5.534126343723901</v>
       </c>
       <c r="E9" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F9" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.2058462838269</v>
+        <v>3.120950021121871</v>
       </c>
       <c r="D10" t="n">
-        <v>18.97676160141831</v>
+        <v>3.083723760230475</v>
       </c>
       <c r="E10" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F10" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.8408754364914</v>
+        <v>8.586642258429853</v>
       </c>
       <c r="D11" t="n">
-        <v>52.6478362386406</v>
+        <v>8.555273388779097</v>
       </c>
       <c r="E11" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F11" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.42548352106797</v>
+        <v>5.756641072173546</v>
       </c>
       <c r="D12" t="n">
-        <v>35.32451844764427</v>
+        <v>5.740234247742195</v>
       </c>
       <c r="E12" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F12" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.31514034731779</v>
+        <v>5.738710306439142</v>
       </c>
       <c r="D13" t="n">
-        <v>28.78485666869483</v>
+        <v>4.67753920866291</v>
       </c>
       <c r="E13" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F13" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>60.70689104133709</v>
+        <v>9.864869794217277</v>
       </c>
       <c r="D14" t="n">
-        <v>4.031128874149275</v>
+        <v>0.6550584420492571</v>
       </c>
       <c r="E14" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F14" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.78966391408932</v>
+        <v>6.140820386039514</v>
       </c>
       <c r="D15" t="n">
-        <v>38.5161682211786</v>
+        <v>6.258877335941522</v>
       </c>
       <c r="E15" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F15" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.59662980865759</v>
+        <v>5.946952343906858</v>
       </c>
       <c r="D16" t="n">
-        <v>36.57467286604026</v>
+        <v>5.943384340731543</v>
       </c>
       <c r="E16" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F16" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.66379416865503</v>
+        <v>6.932866552406443</v>
       </c>
       <c r="D17" t="n">
-        <v>35.96814045454616</v>
+        <v>5.844822823863751</v>
       </c>
       <c r="E17" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F17" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>55.19146824623375</v>
+        <v>8.968613590012986</v>
       </c>
       <c r="D18" t="n">
-        <v>55.94966058339669</v>
+        <v>9.091819844801961</v>
       </c>
       <c r="E18" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F18" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.30321883540048</v>
+        <v>7.036773060752578</v>
       </c>
       <c r="D19" t="n">
-        <v>43.84829190325585</v>
+        <v>7.125347434279075</v>
       </c>
       <c r="E19" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F19" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>54.14473226995172</v>
+        <v>8.798518993867155</v>
       </c>
       <c r="D20" t="n">
-        <v>54.88573134727845</v>
+        <v>8.918931343932748</v>
       </c>
       <c r="E20" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F20" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>52.82886446944765</v>
+        <v>8.584690476285244</v>
       </c>
       <c r="D21" t="n">
-        <v>53.2232559536469</v>
+        <v>8.64877909246762</v>
       </c>
       <c r="E21" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F21" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>56.83743539255128</v>
+        <v>9.236083251289584</v>
       </c>
       <c r="D22" t="n">
-        <v>57.47169571548655</v>
+        <v>9.339150553766565</v>
       </c>
       <c r="E22" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F22" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>65.35154683812202</v>
+        <v>10.61962636119483</v>
       </c>
       <c r="D23" t="n">
-        <v>66.10327154342329</v>
+        <v>10.74178162580628</v>
       </c>
       <c r="E23" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F23" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>63.71440202677181</v>
+        <v>10.35359032935042</v>
       </c>
       <c r="D24" t="n">
-        <v>64.20863824994291</v>
+        <v>10.43390371561572</v>
       </c>
       <c r="E24" t="n">
-        <v>17.77788392734786</v>
+        <v>2.888906138194028</v>
       </c>
       <c r="F24" t="n">
-        <v>18.95036150901257</v>
+        <v>3.079433745214543</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
